--- a/clustering/12 subclusters (factoriescap_s (costs) 0).xlsx
+++ b/clustering/12 subclusters (factoriescap_s (costs) 0).xlsx
@@ -1078,54 +1078,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C42:E42">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C38:E38">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C34:E34">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32:E32">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/clustering/12 subclusters (factoriescap_s (costs) 0).xlsx
+++ b/clustering/12 subclusters (factoriescap_s (costs) 0).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="6">
   <si>
     <t>clust</t>
   </si>
@@ -35,6 +35,9 @@
   <si>
     <t>trainingcosts_s</t>
   </si>
+  <si>
+    <t>Медианы кластеров</t>
+  </si>
 </sst>
 </file>
 
@@ -45,7 +48,7 @@
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +66,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -103,7 +115,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -120,6 +132,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -424,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -1029,9 +1042,133 @@
         <v>4.8776674585716338</v>
       </c>
     </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>0</v>
+      </c>
+      <c r="B47" s="3">
+        <v>13858386.5</v>
+      </c>
+      <c r="C47" s="3">
+        <v>33565.597076099992</v>
+      </c>
+      <c r="D47" s="3">
+        <v>5021.2710237600004</v>
+      </c>
+      <c r="E47" s="3">
+        <v>9.3762416399997388</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>1</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1368960.9999999939</v>
+      </c>
+      <c r="C48" s="3">
+        <v>3010.4278660399891</v>
+      </c>
+      <c r="D48" s="3">
+        <v>6.2364203999998411</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4.571804639999506</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>2</v>
+      </c>
+      <c r="B49" s="3">
+        <v>12161153.999999991</v>
+      </c>
+      <c r="C49" s="3">
+        <v>35568.661953510004</v>
+      </c>
+      <c r="D49" s="3">
+        <v>592.13074661999974</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6413.5022275799993</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>3</v>
+      </c>
+      <c r="B50" s="3">
+        <v>62978040</v>
+      </c>
+      <c r="C50" s="3">
+        <v>220411.94692799999</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1131.9292105</v>
+      </c>
+      <c r="E50" s="3">
+        <v>768.4297439999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>4</v>
+      </c>
+      <c r="B51" s="3">
+        <v>70685379.5</v>
+      </c>
+      <c r="C51" s="3">
+        <v>235399.88781864001</v>
+      </c>
+      <c r="D51" s="3">
+        <v>6773.9100607100017</v>
+      </c>
+      <c r="E51" s="3">
+        <v>633.6145569399996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>5</v>
+      </c>
+      <c r="B52" s="3">
+        <v>7506179.9999999925</v>
+      </c>
+      <c r="C52" s="3">
+        <v>34419.640424399993</v>
+      </c>
+      <c r="D52" s="3">
+        <v>413.53550399999978</v>
+      </c>
+      <c r="E52" s="3">
+        <v>42.596015000000001</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B13">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1043,7 +1180,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C13">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1055,7 +1192,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D13">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1067,7 +1204,55 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E13">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B52">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47:C52">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47:D52">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47:E52">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
